--- a/data/Cases by Product.xlsx
+++ b/data/Cases by Product.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -439,70 +439,98 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CD Whole Gallons</t>
+          <t>Vitamin D</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CD Half Pints</t>
+          <t>2% Red Fat</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>WF Gallons</t>
+          <t>1% Lowfat</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CD Half-Gallons</t>
+          <t>Fat Free</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cedar Cr Gallons</t>
+          <t>Chocolate</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>WF Half-Gallons</t>
+          <t>Strawberry</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CD Quarts</t>
+          <t>Fat Free Chocolate</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CD Pints</t>
+          <t>Whipping Cream</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>5-Gal Foodservice</t>
+          <t>Ice Cream Mix</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Country Dairy Mix</t>
+          <t>Soft Serve Mix</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Butter-Salted</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Butter-Unsalted</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Sour Cream &amp; Chip Dip</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Other (eggnog, co-packed)</t>
         </is>
       </c>
     </row>

--- a/data/Cases by Product.xlsx
+++ b/data/Cases by Product.xlsx
@@ -495,7 +495,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ice Cream Mix</t>
+          <t>Ice Cream</t>
         </is>
       </c>
     </row>
